--- a/Templates/Template_SA-1_Scheda_di_dominio_funzionale.xlsx
+++ b/Templates/Template_SA-1_Scheda_di_dominio_funzionale.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SA-1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'SA-1'!$A$1:$G$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'SA-1'!$A$1:$G$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -863,45 +863,45 @@
       <c r="F22" s="10" t="n"/>
       <c r="G22" s="8" t="n"/>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Sezioni e clausole escluse</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>es. 3.11.6.3 (ADR-nnn): voci delle sezioni principali che il dominio non traccia, ciascuna con la sua ADR di esclusione</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="8" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Relazioni</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="8" t="n"/>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Funzioni di sistema</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Calcolato da ATLAS: SF-DFnn-01 … (catalogo SA-2)</t>
-        </is>
-      </c>
+      <c r="B25" s="10" t="n"/>
       <c r="C25" s="10" t="n"/>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
       <c r="F25" s="10" t="n"/>
       <c r="G25" s="8" t="n"/>
     </row>
-    <row r="26" ht="41" customHeight="1">
+    <row r="26" ht="28" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Dati prodotti/posseduti dal dominio</t>
+          <t>Funzioni di sistema</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Calcolato da ATLAS dagli scambi (SA-5): i dati logici che solo questo dominio produce</t>
+          <t>Calcolato da ATLAS: SF-DFnn-01 … (catalogo SA-2)</t>
         </is>
       </c>
       <c r="C26" s="10" t="n"/>
@@ -910,15 +910,15 @@
       <c r="F26" s="10" t="n"/>
       <c r="G26" s="8" t="n"/>
     </row>
-    <row r="27" ht="28" customHeight="1">
+    <row r="27" ht="41" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Dati usati da altri domini</t>
+          <t>Dati prodotti/posseduti dal dominio</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Calcolato da ATLAS: dato (dominio produttore, scambio FE)</t>
+          <t>Calcolato da ATLAS dagli scambi (SA-5): i dati logici che solo questo dominio produce</t>
         </is>
       </c>
       <c r="C27" s="10" t="n"/>
@@ -930,12 +930,12 @@
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Componenti logici previsti</t>
+          <t>Dati usati da altri domini</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>LC-nn, …</t>
+          <t>Calcolato da ATLAS: dato (dominio produttore, scambio FE)</t>
         </is>
       </c>
       <c r="C28" s="10" t="n"/>
@@ -944,89 +944,97 @@
       <c r="F28" s="10" t="n"/>
       <c r="G28" s="8" t="n"/>
     </row>
-    <row r="29" ht="22" customHeight="1">
+    <row r="29" ht="28" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Decisioni architetturali (ADR) · calcolato da ATLAS: le ADR che riguardano il dominio</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="n"/>
+          <t>Componenti logici previsti</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>LC-nn, …</t>
+        </is>
+      </c>
       <c r="C29" s="10" t="n"/>
       <c r="D29" s="10" t="n"/>
       <c r="E29" s="10" t="n"/>
       <c r="F29" s="10" t="n"/>
       <c r="G29" s="8" t="n"/>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Decisioni architetturali (ADR) · calcolato da ATLAS: le ADR che riguardano il dominio</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="8" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Esito</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>Titolo</t>
         </is>
       </c>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>Decisione DA</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>Attiva</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>ADR-nnn</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>Titolo della decisione</t>
         </is>
       </c>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Proposta</t>
         </is>
       </c>
-      <c r="G31" s="11" t="n"/>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="12" t="n"/>
-      <c r="B32" s="12" t="n"/>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="12" t="n"/>
-      <c r="G32" s="12" t="n"/>
+      <c r="G32" s="11" t="n"/>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="12" t="n"/>
@@ -1037,29 +1045,21 @@
       <c r="F33" s="12" t="n"/>
       <c r="G33" s="12" t="n"/>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="13" t="inlineStr">
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="12" t="n"/>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="12" t="n"/>
+      <c r="G34" s="12" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>Checklist di compilazione di SA-1</t>
         </is>
       </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Lo scopo è una frase (D1)</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="8" t="n"/>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="14" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Nessun dato ha due produttori (D10)</t>
+          <t>Lo scopo è una frase (D1)</t>
         </is>
       </c>
       <c r="C37" s="10" t="n"/>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Ogni interfaccia verso altri domini è uno scambio FE registrato (SA-5)</t>
+          <t>Nessun dato ha due produttori (D10)</t>
         </is>
       </c>
       <c r="C38" s="10" t="n"/>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Le sezioni SRS del dominio compaiono nella matrice sezioni vs domini</t>
+          <t>Ogni interfaccia verso altri domini è uno scambio FE registrato (SA-5)</t>
         </is>
       </c>
       <c r="C39" s="10" t="n"/>
@@ -1112,31 +1112,49 @@
       <c r="F39" s="10" t="n"/>
       <c r="G39" s="8" t="n"/>
     </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Le sezioni SRS del dominio compaiono nella matrice sezioni vs domini</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="8" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="34">
+    <mergeCell ref="C34:D34"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="C30:D30"/>
     <mergeCell ref="B14:G14"/>
     <mergeCell ref="C33:D33"/>
-    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="B23:G23"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A29:G29"/>
     <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B29:G29"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="B38:G38"/>
     <mergeCell ref="B28:G28"/>
     <mergeCell ref="B37:G37"/>
-    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="B40:G40"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="F8:G8"/>
+    <mergeCell ref="A36:G36"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B36:G36"/>
     <mergeCell ref="B26:G26"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="B25:G25"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="B22:G22"/>
     <mergeCell ref="A3:G3"/>
